--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-09T19:03:04Z</t>
+          <t>2026-07-04T11:16:12Z</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-13T17:20:51Z</t>
+          <t>2026-06-29T10:27:34Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-06-13T17:20:45Z</t>
+          <t>2026-07-02T18:14:57Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-22T20:40:29Z</t>
+          <t>2026-07-03T02:41:27Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-06-28T08:03:45Z</t>
+          <t>2026-07-04T11:09:27Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-05-28T08:16:37Z</t>
+          <t>2026-06-28T19:19:53Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-28T08:16:33Z</t>
+          <t>2026-06-28T19:19:49Z</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-05-30T10:02:36Z</t>
+          <t>2026-07-05T07:18:40Z</t>
         </is>
       </c>
       <c r="L95" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-06-29T10:27:34Z</t>
+          <t>2026-07-08T12:27:14Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-02T18:14:57Z</t>
+          <t>2026-07-11T12:35:21Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-03T02:41:27Z</t>
+          <t>2026-07-11T08:24:20Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-04T11:09:27Z</t>
+          <t>2026-07-11T19:49:10Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-26T05:14:07Z</t>
+          <t>2026-07-05T16:18:07Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-06-28T08:36:23Z</t>
+          <t>2026-07-12T07:42:04Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>934</v>
+        <v>973</v>
       </c>
     </row>
     <row r="80">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-04-25T15:48:50Z</t>
+          <t>2026-07-07T18:05:47Z</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-05-02T20:32:27Z</t>
+          <t>2026-07-12T05:23:14Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-17T16:00:19Z</t>
+          <t>2026-07-18T20:11:16Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-23T20:30:07Z</t>
+          <t>2026-07-13T15:47:29Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-05-24T08:27:37Z</t>
+          <t>2026-07-19T05:48:36Z</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-05T16:18:07Z</t>
+          <t>2026-07-12T21:41:06Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-12T07:42:04Z</t>
+          <t>2026-07-19T08:20:06Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>973</v>
+        <v>981</v>
       </c>
     </row>
     <row r="80">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1357,16 +1357,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-23T20:26:54Z</t>
+          <t>2026-07-20T16:42:13Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-23T20:26:50Z</t>
+          <t>2026-07-20T16:42:09Z</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-17T13:04:27Z</t>
+          <t>2026-07-23T15:42:12Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2425,28 +2425,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ovis</t>
+          <t>text2midi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/ovis</t>
+          <t>https://github.com/pinokiofactory/text2midi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:10Z</t>
+          <t>2024-12-27T18:31:20Z</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-01T19:45:35Z</t>
+          <t>2024-12-27T19:21:42Z</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-12-01T17:31:27Z</t>
+          <t>2024-12-27T19:21:39Z</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -2454,53 +2454,53 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>AIDC-AI/Ovis-Image</t>
+          <t>AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AIDC-AI/Ovis-Image</t>
+          <t>https://github.com/AMAAI-Lab/Text2midi</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2025-11-18T03:46:26Z</t>
+          <t>2024-12-19T07:51:33Z</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-04-25T18:06:06Z</t>
+          <t>2026-07-23T14:04:45Z</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>text2midi</t>
+          <t>ovis</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/text2midi</t>
+          <t>https://github.com/pinokiofactory/ovis</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2024-12-27T18:31:20Z</t>
+          <t>2025-12-01T17:31:10Z</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:42Z</t>
+          <t>2025-12-01T19:45:35Z</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2024-12-27T19:21:39Z</t>
+          <t>2025-12-01T17:31:27Z</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2508,26 +2508,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AMAAI-Lab/Text2midi</t>
+          <t>ATH-MaaS/Ovis-Image</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMAAI-Lab/Text2midi</t>
+          <t>https://github.com/ATH-MaaS/Ovis-Image</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2024-12-19T07:51:33Z</t>
+          <t>2025-11-18T03:46:26Z</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-04-06T21:09:10Z</t>
+          <t>2026-07-21T06:35:12Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-06-28T09:20:01Z</t>
+          <t>2026-07-26T08:30:15Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4167</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="58">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-04-17T03:43:29Z</t>
+          <t>2026-07-12T20:11:55Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-19T05:48:36Z</t>
+          <t>2026-07-25T21:13:56Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -2801,11 +2801,11 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-05-03T07:12:35Z</t>
+          <t>2026-07-26T07:05:26Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="61">
@@ -2855,11 +2855,11 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-06-27T21:00:17Z</t>
+          <t>2026-07-26T01:39:59Z</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-05-03T06:49:04Z</t>
+          <t>2026-07-22T10:35:24Z</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-03T04:35:06Z</t>
+          <t>2026-07-25T15:03:27Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3021,11 +3021,11 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-11T12:35:21Z</t>
+          <t>2026-07-23T19:57:10Z</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-05-02T00:10:01Z</t>
+          <t>2026-07-19T06:05:32Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-05-03T06:13:38Z</t>
+          <t>2026-07-26T06:53:50Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-05-03T06:13:38Z</t>
+          <t>2026-07-26T06:53:50Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-04-30T02:46:00Z</t>
+          <t>2026-07-25T18:39:58Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-11T19:49:10Z</t>
+          <t>2026-07-25T22:12:03Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -3353,11 +3353,11 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-05-30T10:02:43Z</t>
+          <t>2026-07-25T20:46:45Z</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-05-03T05:20:18Z</t>
+          <t>2026-07-25T22:50:43Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-06-19T16:17:29Z</t>
+          <t>2026-07-26T01:41:05Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3523,11 +3523,11 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-05-02T20:48:54Z</t>
+          <t>2026-07-24T02:03:59Z</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-06-27T11:48:22Z</t>
+          <t>2026-07-20T13:02:16Z</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-05-02T23:23:36Z</t>
+          <t>2026-07-26T00:01:32Z</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="76">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-05-02T09:43:14Z</t>
+          <t>2026-07-21T04:21:39Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3743,11 +3743,11 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-06-13T15:05:55Z</t>
+          <t>2026-07-12T13:28:32Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-06-04T12:36:42Z</t>
+          <t>2026-07-25T15:44:05Z</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-19T08:20:06Z</t>
+          <t>2026-07-26T00:09:49Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>981</v>
+        <v>997</v>
       </c>
     </row>
     <row r="80">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-05-02T15:38:09Z</t>
+          <t>2026-07-23T07:06:48Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3959,11 +3959,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-05-03T05:56:07Z</t>
+          <t>2026-07-25T23:01:14Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-05-03T04:51:58Z</t>
+          <t>2026-07-26T01:02:17Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-05-02T12:49:34Z</t>
+          <t>2026-07-26T05:06:37Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4121,11 +4121,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-05-01T18:11:07Z</t>
+          <t>2026-07-24T07:10:53Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -4175,11 +4175,11 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-05-03T07:35:54Z</t>
+          <t>2026-07-26T04:53:47Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-05-01T11:29:35Z</t>
+          <t>2026-07-26T00:11:40Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-05-31T04:54:18Z</t>
+          <t>2026-07-06T03:28:04Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4341,11 +4341,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-06-17T11:39:32Z</t>
+          <t>2026-07-24T10:48:49Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-06-25T09:16:47Z</t>
+          <t>2026-07-23T14:29:04Z</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -4453,11 +4453,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-06-06T21:18:59Z</t>
+          <t>2026-07-26T08:14:36Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91">
@@ -4507,11 +4507,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-05-17T07:49:42Z</t>
+          <t>2026-07-26T02:42:04Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1144</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="92">
@@ -4561,11 +4561,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-05-03T07:54:03Z</t>
+          <t>2026-07-25T19:21:54Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-05-03T07:41:17Z</t>
+          <t>2026-07-26T08:02:20Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94">
@@ -4669,11 +4669,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-05-31T03:36:41Z</t>
+          <t>2026-07-26T06:31:45Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-05T07:18:40Z</t>
+          <t>2026-07-24T06:20:56Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-04-22T07:48:52Z</t>
+          <t>2026-07-24T19:24:04Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-05-19T12:52:07Z</t>
+          <t>2026-07-24T19:24:04Z</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -4901,11 +4901,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-05-02T17:57:29Z</t>
+          <t>2026-07-26T03:28:06Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-12T05:23:14Z</t>
+          <t>2026-07-26T05:35:20Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="100">
@@ -5009,11 +5009,11 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-05-01T19:29:34Z</t>
+          <t>2026-07-26T06:46:00Z</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-06-21T09:45:00Z</t>
+          <t>2026-07-26T04:01:07Z</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-05-02T21:59:21Z</t>
+          <t>2026-07-26T04:01:07Z</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-30T18:42:28Z</t>
+          <t>2026-07-29T12:26:31Z</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-26T13:30:41Z</t>
+          <t>2026-07-28T09:24:27Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-26T08:30:15Z</t>
+          <t>2026-08-02T08:32:18Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4334</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="58">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -685,12 +685,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-30T18:36:45Z</t>
+          <t>2026-08-04T04:28:00Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-12-02T22:00:10Z</t>
+          <t>2026-08-04T04:27:41Z</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -845,12 +845,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-09T10:15:00Z</t>
+          <t>2026-08-04T06:09:28Z</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-12-02T21:58:14Z</t>
+          <t>2026-08-04T05:04:43Z</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-08T19:47:01Z</t>
+          <t>2026-08-05T13:45:27Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-20T16:42:13Z</t>
+          <t>2026-08-04T23:21:16Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-06T00:01:08Z</t>
+          <t>2026-08-04T09:46:18Z</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-05T19:59:58Z</t>
+          <t>2026-08-05T04:32:11Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-25T15:44:05Z</t>
+          <t>2026-08-08T01:19:13Z</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-12T21:41:06Z</t>
+          <t>2026-08-08T18:12:59Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-29T04:48:55Z</t>
+          <t>2026-08-08T18:12:55Z</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-26T00:09:49Z</t>
+          <t>2026-08-09T05:54:09Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>997</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="80">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:15Z</t>
+          <t>2026-08-04T05:47:53Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-24T19:24:04Z</t>
+          <t>2026-08-08T11:23:19Z</t>
         </is>
       </c>
       <c r="L97" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-05T13:45:27Z</t>
+          <t>2026-08-15T20:09:45Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-23T15:42:12Z</t>
+          <t>2026-08-12T18:15:44Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-18T22:16:08Z</t>
+          <t>2026-08-13T01:59:09Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-28T09:24:27Z</t>
+          <t>2026-08-13T23:51:14Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-02T08:32:18Z</t>
+          <t>2026-08-16T06:45:28Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4384</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="58">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-08T12:27:14Z</t>
+          <t>2026-08-13T21:59:53Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-23T19:57:10Z</t>
+          <t>2026-08-16T03:44:11Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-11T08:24:20Z</t>
+          <t>2026-08-16T03:25:08Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-25T22:12:03Z</t>
+          <t>2026-08-15T20:26:43Z</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-08T23:08:38Z</t>
+          <t>2026-08-13T15:02:42Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-23T19:59:21Z</t>
+          <t>2026-08-13T15:01:39Z</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-12T13:28:32Z</t>
+          <t>2026-08-15T15:31:12Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-08T18:12:59Z</t>
+          <t>2026-08-16T03:03:16Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-08T18:12:55Z</t>
+          <t>2026-08-15T15:40:06Z</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-09T05:54:09Z</t>
+          <t>2026-08-16T05:06:23Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1056</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="80">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-16T07:24:28Z</t>
+          <t>2026-08-23T02:25:30Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2009,16 +2009,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-07T13:14:13Z</t>
+          <t>2026-08-18T12:44:33Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-11-25T11:47:58Z</t>
+          <t>2026-08-18T12:41:09Z</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-13T01:59:09Z</t>
+          <t>2026-08-20T23:47:42Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23T14:04:45Z</t>
+          <t>2026-08-21T07:17:39Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-21T06:35:12Z</t>
+          <t>2026-08-15T14:10:00Z</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-16T06:45:28Z</t>
+          <t>2026-08-23T06:46:49Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4610</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="58">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-12T20:11:55Z</t>
+          <t>2026-08-22T05:54:56Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-25T21:13:56Z</t>
+          <t>2026-08-23T03:37:46Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
@@ -2801,11 +2801,11 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-26T07:05:26Z</t>
+          <t>2026-08-23T02:20:52Z</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-26T01:39:59Z</t>
+          <t>2026-08-16T21:23:04Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22T10:35:24Z</t>
+          <t>2026-08-11T04:43:23Z</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-25T15:03:27Z</t>
+          <t>2026-08-22T17:28:22Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-19T06:05:32Z</t>
+          <t>2026-08-20T21:20:19Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-26T06:53:50Z</t>
+          <t>2026-08-23T06:11:01Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-26T06:53:50Z</t>
+          <t>2026-08-23T06:11:01Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-25T18:39:58Z</t>
+          <t>2026-08-20T00:32:33Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-16T03:25:08Z</t>
+          <t>2026-08-22T00:29:22Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-15T20:26:43Z</t>
+          <t>2026-08-23T06:31:25Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-25T20:46:45Z</t>
+          <t>2026-08-20T21:20:49Z</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-25T22:50:43Z</t>
+          <t>2026-08-23T06:36:11Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-26T01:41:05Z</t>
+          <t>2026-08-21T17:33:03Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-24T02:03:59Z</t>
+          <t>2026-08-22T14:43:35Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-20T13:02:16Z</t>
+          <t>2026-08-21T20:52:20Z</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-26T00:01:32Z</t>
+          <t>2026-08-23T04:58:27Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-21T04:21:39Z</t>
+          <t>2026-08-20T21:21:08Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-08T01:19:13Z</t>
+          <t>2026-08-20T21:20:35Z</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3851,11 +3851,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-16T05:06:23Z</t>
+          <t>2026-08-23T05:30:08Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1089</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="80">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-23T07:06:48Z</t>
+          <t>2026-08-19T09:46:03Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3959,11 +3959,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-25T23:01:14Z</t>
+          <t>2026-08-22T18:22:48Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-26T01:02:17Z</t>
+          <t>2026-08-20T13:08:15Z</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-26T05:06:37Z</t>
+          <t>2026-08-22T14:09:26Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-24T07:10:53Z</t>
+          <t>2026-08-21T20:08:44Z</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -4175,11 +4175,11 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-26T04:53:47Z</t>
+          <t>2026-08-23T06:19:31Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -4229,11 +4229,11 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-26T00:11:40Z</t>
+          <t>2026-08-22T13:23:31Z</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-06T03:28:04Z</t>
+          <t>2026-08-12T17:57:58Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-19T11:53:14Z</t>
+          <t>2026-08-21T07:38:33Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4341,11 +4341,11 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-24T10:48:49Z</t>
+          <t>2026-08-21T19:14:44Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-23T14:29:04Z</t>
+          <t>2026-08-17T03:09:40Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90">
@@ -4453,11 +4453,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-26T08:14:36Z</t>
+          <t>2026-08-23T05:00:32Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="91">
@@ -4507,11 +4507,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-26T02:42:04Z</t>
+          <t>2026-08-23T00:54:38Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1155</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="92">
@@ -4561,11 +4561,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-25T19:21:54Z</t>
+          <t>2026-08-23T05:01:36Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-26T08:02:20Z</t>
+          <t>2026-08-23T06:21:53Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-26T06:31:45Z</t>
+          <t>2026-08-23T06:29:11Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-28T19:19:53Z</t>
+          <t>2026-08-16T19:02:26Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-24T06:20:56Z</t>
+          <t>2026-08-21T05:15:57Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-24T19:24:04Z</t>
+          <t>2026-08-21T01:59:23Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-08T11:23:19Z</t>
+          <t>2026-08-21T01:59:23Z</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -4901,11 +4901,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-26T03:28:06Z</t>
+          <t>2026-08-22T01:15:28Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-26T05:35:20Z</t>
+          <t>2026-08-23T06:27:56Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-26T06:46:00Z</t>
+          <t>2026-08-16T16:11:04Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-26T04:01:07Z</t>
+          <t>2026-08-22T20:58:38Z</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-26T04:01:07Z</t>
+          <t>2026-08-22T20:58:38Z</t>
         </is>
       </c>
       <c r="L102" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -569,12 +569,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-18T20:11:16Z</t>
+          <t>2026-08-28T01:46:33Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-05T21:23:49Z</t>
+          <t>2026-08-28T01:46:28Z</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-18T12:44:33Z</t>
+          <t>2026-08-26T14:34:20Z</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-21T07:17:39Z</t>
+          <t>2026-08-27T14:16:17Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-15T14:10:00Z</t>
+          <t>2026-08-27T10:38:00Z</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-23T06:46:49Z</t>
+          <t>2026-08-30T11:06:14Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4662</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="58">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-22T05:54:56Z</t>
+          <t>2026-08-28T15:45:38Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-23T03:37:46Z</t>
+          <t>2026-08-30T10:22:24Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-23T02:20:52Z</t>
+          <t>2026-08-30T09:54:47Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-22T17:28:22Z</t>
+          <t>2026-08-30T09:22:35Z</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-13T21:59:53Z</t>
+          <t>2026-08-26T03:40:09Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-16T03:44:11Z</t>
+          <t>2026-08-28T06:34:58Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-20T21:20:19Z</t>
+          <t>2026-08-24T12:06:10Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-23T06:11:01Z</t>
+          <t>2026-08-30T11:35:37Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-23T06:11:01Z</t>
+          <t>2026-08-30T11:35:37Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-20T00:32:33Z</t>
+          <t>2026-08-29T07:18:37Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-22T00:29:22Z</t>
+          <t>2026-08-29T02:10:25Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-23T06:31:25Z</t>
+          <t>2026-08-30T07:22:45Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-20T21:20:49Z</t>
+          <t>2026-08-30T08:26:09Z</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-23T06:36:11Z</t>
+          <t>2026-08-30T09:55:42Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3421,198 +3421,194 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MagicQuill</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
-        </is>
-      </c>
+          <t>echomimic2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/MagicQuill</t>
+          <t>https://github.com/pinokiofactory/echomimic2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-02-19T03:58:52Z</t>
+          <t>2024-11-24T07:52:04Z</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-15T00:32:37Z</t>
+          <t>2026-04-28T23:29:48Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-01-11T20:07:58Z</t>
+          <t>2026-04-28T23:29:43Z</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ant-research/MagicQuill</t>
+          <t>antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/ant-research/MagicQuill</t>
+          <t>https://github.com/antgroup/echomimic_v2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2024-11-12T12:52:36Z</t>
+          <t>2024-11-20T08:35:35Z</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-21T17:33:03Z</t>
+          <t>2026-08-30T09:29:03Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>echomimic2</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>macOS-use</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>We Make Mac apps accessible for AI agents</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/echomimic2</t>
+          <t>https://github.com/pinokiofactory/macOS-use</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2024-11-24T07:52:04Z</t>
+          <t>2025-02-18T16:54:37Z</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-28T23:29:48Z</t>
+          <t>2026-08-26T11:39:14Z</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-28T23:29:43Z</t>
+          <t>2025-04-01T04:14:59Z</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>antgroup/echomimic_v2</t>
+          <t>browser-use/macOS-use</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/antgroup/echomimic_v2</t>
+          <t>https://github.com/browser-use/macOS-use</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2024-11-20T08:35:35Z</t>
+          <t>2025-01-23T00:35:15Z</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-22T14:43:35Z</t>
+          <t>2026-08-29T20:15:22Z</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>macOS-use</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>We Make Mac apps accessible for AI agents</t>
-        </is>
-      </c>
+          <t>browser-use</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/macOS-use</t>
+          <t>https://github.com/pinokiofactory/browser-use</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-02-18T16:54:37Z</t>
+          <t>2025-01-19T21:55:50Z</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-06-23T11:41:29Z</t>
+          <t>2026-01-27T14:53:11Z</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-04-01T04:14:59Z</t>
+          <t>2025-04-01T04:25:12Z</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>browser-use/macOS-use</t>
+          <t>browser-use/web-ui</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/macOS-use</t>
+          <t>https://github.com/browser-use/web-ui</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2025-01-23T00:35:15Z</t>
+          <t>2025-01-02T01:29:44Z</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-21T20:52:20Z</t>
+          <t>2026-08-30T09:55:09Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>16</v>
+        <v>323</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>browser-use</t>
+          <t>uno</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/browser-use</t>
+          <t>https://github.com/pinokiofactory/uno</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-01-19T21:55:50Z</t>
+          <t>2025-04-10T18:31:57Z</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-27T14:53:11Z</t>
+          <t>2025-12-02T20:55:29Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-04-01T04:25:12Z</t>
+          <t>2025-12-02T20:55:25Z</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -3620,323 +3616,323 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>browser-use/web-ui</t>
+          <t>bytedance/UNO</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/web-ui</t>
+          <t>https://github.com/bytedance/UNO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2025-01-02T01:29:44Z</t>
+          <t>2025-04-01T13:25:11Z</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-23T04:58:27Z</t>
+          <t>2026-08-20T21:21:08Z</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>323</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>uno</t>
+          <t>Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/uno</t>
+          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-04-10T18:31:57Z</t>
+          <t>2025-01-25T04:44:25Z</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:29Z</t>
+          <t>2026-08-13T15:02:42Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:25Z</t>
+          <t>2026-08-13T15:01:39Z</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>bytedance/UNO</t>
+          <t>deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/UNO</t>
+          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2025-04-01T13:25:11Z</t>
+          <t>2025-01-22T01:50:03Z</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-20T21:21:08Z</t>
+          <t>2026-08-29T21:52:55Z</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hunyuan3d-2-lowvram</t>
+          <t>hunyuanvideo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Hunyuan3d-2-lowvram</t>
+          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-01-25T04:44:25Z</t>
+          <t>2024-12-11T01:55:53Z</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-13T15:02:42Z</t>
+          <t>2026-08-25T05:45:12Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-13T15:01:39Z</t>
+          <t>2025-12-02T20:58:56Z</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Hunyuan3D-2GP</t>
+          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2025-01-22T01:50:03Z</t>
+          <t>2024-12-10T18:34:42Z</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-15T15:31:12Z</t>
+          <t>2026-08-27T06:36:32Z</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>hunyuanvideo</t>
+          <t>wan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/hunyuanvideo</t>
+          <t>https://github.com/pinokiofactory/wan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2024-12-11T01:55:53Z</t>
+          <t>2025-03-03T17:32:45Z</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-05T04:32:11Z</t>
+          <t>2026-08-24T03:03:44Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-12-02T20:58:56Z</t>
+          <t>2026-08-15T15:40:06Z</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>deepbeepmeep/HunyuanVideoGP</t>
+          <t>deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/HunyuanVideoGP</t>
+          <t>https://github.com/deepbeepmeep/Wan2GP</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2024-12-10T18:34:42Z</t>
+          <t>2025-02-27T23:52:36Z</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-20T21:20:35Z</t>
+          <t>2026-08-30T11:26:02Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>13</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>wan</t>
+          <t>yue</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/wan</t>
+          <t>https://github.com/pinokiofactory/yue</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-03-03T17:32:45Z</t>
+          <t>2025-01-29T11:22:39Z</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-16T03:03:16Z</t>
+          <t>2026-02-11T18:06:59Z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-15T15:40:06Z</t>
+          <t>2025-12-02T21:56:04Z</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>deepbeepmeep/Wan2GP</t>
+          <t>deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/Wan2GP</t>
+          <t>https://github.com/deepbeepmeep/YuEGP</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-02-27T23:52:36Z</t>
+          <t>2025-01-28T07:23:51Z</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-23T05:30:08Z</t>
+          <t>2026-08-19T09:46:03Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1122</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>yue</t>
+          <t>janus</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/yue</t>
+          <t>https://github.com/pinokiofactory/janus</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-01-29T11:22:39Z</t>
+          <t>2025-01-27T18:23:47Z</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-11T18:06:59Z</t>
+          <t>2025-01-28T02:37:49Z</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-12-02T21:56:04Z</t>
+          <t>2025-01-28T02:37:46Z</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>deepbeepmeep/YuEGP</t>
+          <t>deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepbeepmeep/YuEGP</t>
+          <t>https://github.com/deepseek-ai/Janus</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-01-28T07:23:51Z</t>
+          <t>2024-10-18T03:48:16Z</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-19T09:46:03Z</t>
+          <t>2026-08-29T17:21:17Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>janus</t>
+          <t>diamond</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/janus</t>
+          <t>https://github.com/pinokiofactory/diamond</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-01-27T18:23:47Z</t>
+          <t>2024-10-12T15:37:19Z</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:49Z</t>
+          <t>2026-01-24T06:17:09Z</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-01-28T02:37:46Z</t>
+          <t>2025-12-02T23:46:49Z</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -3944,601 +3940,601 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>deepseek-ai/Janus</t>
+          <t>eloialonso/diamond</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/deepseek-ai/Janus</t>
+          <t>https://github.com/eloialonso/diamond</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2024-10-18T03:48:16Z</t>
+          <t>2024-05-19T22:31:40Z</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-22T18:22:48Z</t>
+          <t>2026-08-27T18:39:50Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>diamond</t>
+          <t>AllTalk-TTS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/diamond</t>
+          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2024-10-12T15:37:19Z</t>
+          <t>2025-02-05T16:24:30Z</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-24T06:17:09Z</t>
+          <t>2025-04-05T16:19:34Z</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-12-02T23:46:49Z</t>
+          <t>2025-03-29T16:44:51Z</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>eloialonso/diamond</t>
+          <t>erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/eloialonso/diamond</t>
+          <t>https://github.com/erew123/alltalk_tts</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2024-05-19T22:31:40Z</t>
+          <t>2023-12-08T09:35:19Z</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-20T13:08:15Z</t>
+          <t>2026-08-26T15:05:34Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AllTalk-TTS</t>
+          <t>oasis</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/AllTalk-TTS</t>
+          <t>https://github.com/pinokiofactory/oasis</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-02-05T16:24:30Z</t>
+          <t>2024-10-31T23:24:32Z</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-04-05T16:19:34Z</t>
+          <t>2024-10-31T23:47:38Z</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-03-29T16:44:51Z</t>
+          <t>2024-10-31T23:47:35Z</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>erew123/alltalk_tts</t>
+          <t>etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/erew123/alltalk_tts</t>
+          <t>https://github.com/etched-ai/open-oasis</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2023-12-08T09:35:19Z</t>
+          <t>2024-10-31T09:10:45Z</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-22T14:09:26Z</t>
+          <t>2026-08-24T11:18:53Z</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>oasis</t>
+          <t>openaudio</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/oasis</t>
+          <t>https://github.com/pinokiofactory/openaudio</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2024-10-31T23:24:32Z</t>
+          <t>2024-11-02T08:47:31Z</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:38Z</t>
+          <t>2026-04-28T21:58:57Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-10-31T23:47:35Z</t>
+          <t>2026-04-25T02:45:14Z</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>etched-ai/open-oasis</t>
+          <t>fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/etched-ai/open-oasis</t>
+          <t>https://github.com/fishaudio/fish-speech</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2024-10-31T09:10:45Z</t>
+          <t>2023-10-10T03:16:51Z</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-21T20:08:44Z</t>
+          <t>2026-08-30T11:16:43Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>openaudio</t>
+          <t>mochi</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/openaudio</t>
+          <t>https://github.com/pinokiofactory/mochi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2024-11-02T08:47:31Z</t>
+          <t>2024-10-23T18:51:07Z</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-04-28T21:58:57Z</t>
+          <t>2024-10-29T03:03:08Z</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-25T02:45:14Z</t>
+          <t>2024-10-29T03:03:04Z</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>fishaudio/fish-speech</t>
+          <t>genmoai/mochi</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/fishaudio/fish-speech</t>
+          <t>https://github.com/genmoai/mochi</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2023-10-10T03:16:51Z</t>
+          <t>2024-09-11T02:55:33Z</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-23T06:19:31Z</t>
+          <t>2026-08-30T06:46:41Z</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mochi</t>
+          <t>instantir</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/mochi</t>
+          <t>https://github.com/pinokiofactory/instantir</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2024-10-23T18:51:07Z</t>
+          <t>2024-11-08T08:05:55Z</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:08Z</t>
+          <t>2026-05-28T03:05:24Z</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2024-10-29T03:03:04Z</t>
+          <t>2026-05-28T03:05:19Z</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>genmoai/mochi</t>
+          <t>instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/genmoai/mochi</t>
+          <t>https://github.com/instantX-research/InstantIR</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2024-09-11T02:55:33Z</t>
+          <t>2024-10-20T03:17:01Z</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-22T13:23:31Z</t>
+          <t>2026-08-12T17:57:58Z</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>instantir</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>whisper-webui</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pinokio Installer for Whisper-Webui</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/instantir</t>
+          <t>https://github.com/pinokiofactory/whisper-webui</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2024-11-08T08:05:55Z</t>
+          <t>2024-09-21T20:42:20Z</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-28T03:05:24Z</t>
+          <t>2026-08-25T19:36:03Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-28T03:05:19Z</t>
+          <t>2026-08-25T19:35:58Z</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>instantX-research/InstantIR</t>
+          <t>jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/instantX-research/InstantIR</t>
+          <t>https://github.com/jhj0517/Whisper-WebUI</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2024-10-20T03:17:01Z</t>
+          <t>2023-03-02T13:42:01Z</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-12T17:57:58Z</t>
+          <t>2026-08-30T08:25:53Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>8</v>
+        <v>156</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>whisper-webui</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Pinokio Installer for Whisper-Webui</t>
-        </is>
-      </c>
+          <t>pyramidflow</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/whisper-webui</t>
+          <t>https://github.com/pinokiofactory/pyramidflow</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2024-09-21T20:42:20Z</t>
+          <t>2024-11-16T08:35:22Z</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T07:38:33Z</t>
+          <t>2026-06-23T16:22:14Z</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-23T20:32:48Z</t>
+          <t>2026-05-25T01:05:35Z</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>jhj0517/Whisper-WebUI</t>
+          <t>jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jhj0517/Whisper-WebUI</t>
+          <t>https://github.com/jy0205/Pyramid-Flow</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2023-03-02T13:42:01Z</t>
+          <t>2024-10-06T13:06:31Z</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-21T19:14:44Z</t>
+          <t>2026-08-28T23:28:06Z</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>pyramidflow</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>Frame-Pack</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/pyramidflow</t>
+          <t>https://github.com/pinokiofactory/Frame-Pack</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2024-11-16T08:35:22Z</t>
+          <t>2025-04-17T11:43:03Z</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-23T16:22:14Z</t>
+          <t>2026-06-05T19:56:54Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-25T01:05:35Z</t>
+          <t>2026-05-24T02:17:30Z</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>jy0205/Pyramid-Flow</t>
+          <t>lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/jy0205/Pyramid-Flow</t>
+          <t>https://github.com/lllyasviel/FramePack</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2024-10-06T13:06:31Z</t>
+          <t>2025-04-12T14:45:22Z</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-17T03:09:40Z</t>
+          <t>2026-08-29T20:10:49Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>73</v>
+        <v>488</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Frame-Pack</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>(NVIDIA) FramePack is a next-frame (next-frame-section) prediction neural network structure that generates videos progressively.</t>
-        </is>
-      </c>
+          <t>stable-diffusion-webui-forge</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Frame-Pack</t>
+          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-04-17T11:43:03Z</t>
+          <t>2024-08-12T12:38:49Z</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-05T19:56:54Z</t>
+          <t>2026-05-15T18:54:36Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-24T02:17:30Z</t>
+          <t>2026-04-28T22:51:44Z</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>lllyasviel/FramePack</t>
+          <t>lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/FramePack</t>
+          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-04-12T14:45:22Z</t>
+          <t>2024-01-14T11:39:30Z</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-23T05:00:32Z</t>
+          <t>2026-08-30T09:54:25Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>487</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>stable-diffusion-webui-forge</t>
+          <t>omniparser</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/stable-diffusion-webui-forge</t>
+          <t>https://github.com/pinokiofactory/omniparser</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2024-08-12T12:38:49Z</t>
+          <t>2024-10-26T06:04:17Z</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-05-15T18:54:36Z</t>
+          <t>2024-10-28T04:49:07Z</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-28T22:51:44Z</t>
+          <t>2024-10-26T08:03:10Z</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>lllyasviel/stable-diffusion-webui-forge</t>
+          <t>microsoft/OmniParser</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/lllyasviel/stable-diffusion-webui-forge</t>
+          <t>https://github.com/microsoft/OmniParser</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2024-01-14T11:39:30Z</t>
+          <t>2024-09-20T05:18:18Z</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-23T00:54:38Z</t>
+          <t>2026-08-30T11:15:30Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1157</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>omniparser</t>
+          <t>vibevoice-realtime</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/omniparser</t>
+          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2024-10-26T06:04:17Z</t>
+          <t>2025-12-04T21:57:09Z</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2024-10-28T04:49:07Z</t>
+          <t>2026-08-26T22:44:45Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2024-10-26T08:03:10Z</t>
+          <t>2026-08-24T16:30:34Z</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4546,227 +4542,231 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>microsoft/OmniParser</t>
+          <t>microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/OmniParser</t>
+          <t>https://github.com/microsoft/VibeVoice</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2024-09-20T05:18:18Z</t>
+          <t>2025-08-25T13:24:01Z</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-23T05:01:36Z</t>
+          <t>2026-08-30T11:32:42Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>230</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>vibevoice-realtime</t>
+          <t>dia</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/vibevoice-realtime</t>
+          <t>https://github.com/pinokiofactory/dia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-12-04T21:57:09Z</t>
+          <t>2025-04-22T14:57:53Z</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-30T14:45:13Z</t>
+          <t>2026-05-25T00:57:28Z</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-12-22T22:00:09Z</t>
+          <t>2026-05-25T00:57:23Z</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>microsoft/VibeVoice</t>
+          <t>nari-labs/dia</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/VibeVoice</t>
+          <t>https://github.com/nari-labs/dia</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2025-08-25T13:24:01Z</t>
+          <t>2025-04-19T07:15:57Z</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-23T06:21:53Z</t>
+          <t>2026-08-29T17:18:06Z</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>183</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dia</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>clarity-refiners-ui</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/dia</t>
+          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-04-22T14:57:53Z</t>
+          <t>2024-11-12T07:03:48Z</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-05-25T00:57:28Z</t>
+          <t>2026-08-16T19:02:26Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-25T00:57:23Z</t>
+          <t>2026-06-28T19:19:49Z</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>nari-labs/dia</t>
+          <t>philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/nari-labs/dia</t>
+          <t>https://github.com/philz1337x/clarity-upscaler</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2025-04-19T07:15:57Z</t>
+          <t>2024-03-15T15:21:40Z</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-23T06:29:11Z</t>
+          <t>2026-08-29T11:42:38Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>clarity-refiners-ui</t>
+          <t>Allegro-txt2vid</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Creative Image Enhancer/Upscaler. Powered By Refiners.  8GB VRAM | 10GB Install</t>
+          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/clarity-refiners-ui</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2024-11-12T07:03:48Z</t>
+          <t>2024-10-25T06:33:03Z</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-16T19:02:26Z</t>
+          <t>2024-11-05T23:56:50Z</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-28T19:19:49Z</t>
+          <t>2024-11-05T23:56:47Z</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>philz1337x/clarity-upscaler</t>
+          <t>rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/philz1337x/clarity-upscaler</t>
+          <t>https://github.com/rhymes-ai/Allegro</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2024-03-15T15:21:40Z</t>
+          <t>2024-10-16T04:04:15Z</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-08-21T05:15:57Z</t>
+          <t>2026-08-26T22:00:13Z</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid</t>
+          <t>Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Allegro is a powerful text-to-video model that generates high-quality videos up to 6 seconds at 15 FPS and 720p resolution from simple text input.</t>
+          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid</t>
+          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2024-10-25T06:33:03Z</t>
+          <t>2024-10-27T14:58:05Z</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:50Z</t>
+          <t>2026-08-04T05:47:53Z</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2024-11-05T23:56:47Z</t>
+          <t>2026-05-26T19:25:11Z</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-21T01:59:23Z</t>
+          <t>2026-08-26T22:00:13Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4795,59 +4795,59 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid-install</t>
+          <t>MagicQuill</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Allegro-txt2vid. WARNING: takes a long time to generate a result, 1hr on a 3090. 12GB+ VRAM | 32GB+ RAM | 30GB Download. Check the README for details</t>
+          <t>An intelligent, interactive Image Editing System. Easily erase and add objects on a user-friendly interface.</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/pinokiofactory/Allegro-txt2vid-install</t>
+          <t>https://github.com/pinokiofactory/MagicQuill</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2024-10-27T14:58:05Z</t>
+          <t>2025-02-19T03:58:52Z</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-04T05:47:53Z</t>
+          <t>2026-06-15T00:32:37Z</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-26T19:25:11Z</t>
+          <t>2026-01-11T20:07:58Z</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>rhymes-ai/Allegro</t>
+          <t>robbyant-research/MagicQuill</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/rhymes-ai/Allegro</t>
+          <t>https://github.com/robbyant-research/MagicQuill</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2024-10-16T04:04:15Z</t>
+          <t>2024-11-12T12:52:36Z</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-21T01:59:23Z</t>
+          <t>2026-08-28T15:27:27Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-22T01:15:28Z</t>
+          <t>2026-08-29T22:05:32Z</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-23T06:27:56Z</t>
+          <t>2026-08-30T09:16:55Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-21T05:04:02Z</t>
+          <t>2026-08-28T03:34:13Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-01T02:35:24Z</t>
+          <t>2026-08-28T03:33:37Z</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-22T20:58:38Z</t>
+          <t>2026-08-30T10:17:25Z</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-08-22T20:58:38Z</t>
+          <t>2026-08-30T10:17:25Z</t>
         </is>
       </c>
       <c r="L102" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-24T03:03:44Z</t>
+          <t>2026-09-03T13:06:32Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-30T11:26:02Z</t>
+          <t>2026-09-06T10:29:35Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1151</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="79">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-25T19:36:03Z</t>
+          <t>2026-09-05T16:10:36Z</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4283,11 +4283,11 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-30T08:25:53Z</t>
+          <t>2026-09-05T21:35:10Z</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-05-15T18:54:36Z</t>
+          <t>2026-09-04T00:04:32Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-28T22:51:44Z</t>
+          <t>2026-09-04T00:04:28Z</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-30T09:54:25Z</t>
+          <t>2026-09-06T10:11:47Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="91">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-26T22:44:45Z</t>
+          <t>2026-09-03T03:45:34Z</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-24T16:30:34Z</t>
+          <t>2026-09-03T03:45:30Z</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4557,11 +4557,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-30T11:32:42Z</t>
+          <t>2026-09-06T10:34:41Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-28T03:34:13Z</t>
+          <t>2026-09-05T21:47:20Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-30T10:17:25Z</t>
+          <t>2026-09-06T04:54:57Z</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-15T20:09:45Z</t>
+          <t>2026-09-13T02:39:48Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:21:16Z</t>
+          <t>2026-09-09T20:45:26Z</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-27T14:16:17Z</t>
+          <t>2026-09-07T18:34:43Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-30T11:06:14Z</t>
+          <t>2026-09-13T11:33:08Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4751</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="58">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-28T15:45:38Z</t>
+          <t>2026-09-04T05:41:49Z</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-30T10:22:24Z</t>
+          <t>2026-09-13T11:12:17Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-30T09:54:47Z</t>
+          <t>2026-09-13T09:41:57Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-16T21:23:04Z</t>
+          <t>2026-09-12T01:57:37Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-30T09:22:35Z</t>
+          <t>2026-09-12T19:22:09Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-24T12:06:10Z</t>
+          <t>2026-09-07T08:51:10Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-30T11:35:37Z</t>
+          <t>2026-09-13T11:29:36Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-30T11:35:37Z</t>
+          <t>2026-09-13T11:29:36Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-29T07:18:37Z</t>
+          <t>2026-09-10T07:30:34Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-30T07:22:45Z</t>
+          <t>2026-09-13T00:51:49Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-30T08:26:09Z</t>
+          <t>2026-09-12T12:39:59Z</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-30T09:55:42Z</t>
+          <t>2026-09-13T05:42:32Z</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-30T09:29:03Z</t>
+          <t>2026-09-13T09:42:36Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-29T20:15:22Z</t>
+          <t>2026-09-13T10:42:07Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-30T09:55:09Z</t>
+          <t>2026-09-13T10:40:04Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="75">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-20T21:21:08Z</t>
+          <t>2026-09-04T05:42:21Z</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-29T21:52:55Z</t>
+          <t>2026-09-04T07:02:36Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-27T06:36:32Z</t>
+          <t>2026-09-06T21:10:55Z</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-06T10:29:35Z</t>
+          <t>2026-09-13T10:28:53Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1168</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="79">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-19T09:46:03Z</t>
+          <t>2026-09-12T17:39:19Z</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-29T17:21:17Z</t>
+          <t>2026-09-13T08:38:23Z</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-27T18:39:50Z</t>
+          <t>2026-09-12T17:52:41Z</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-26T15:05:34Z</t>
+          <t>2026-09-10T10:56:15Z</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-24T11:18:53Z</t>
+          <t>2026-09-11T01:17:35Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4117,11 +4117,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-30T11:16:43Z</t>
+          <t>2026-09-13T08:09:59Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-30T06:46:41Z</t>
+          <t>2026-09-12T17:48:03Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-12T17:57:58Z</t>
+          <t>2026-09-04T10:12:02Z</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-05T21:35:10Z</t>
+          <t>2026-09-11T16:05:24Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-28T23:28:06Z</t>
+          <t>2026-09-08T03:34:53Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-29T20:10:49Z</t>
+          <t>2026-09-12T21:23:03Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-06T10:11:47Z</t>
+          <t>2026-09-13T07:37:37Z</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-30T11:15:30Z</t>
+          <t>2026-09-13T07:02:11Z</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -4557,11 +4557,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-06T10:34:41Z</t>
+          <t>2026-09-13T09:27:29Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-29T17:18:06Z</t>
+          <t>2026-09-12T20:21:58Z</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-29T11:42:38Z</t>
+          <t>2026-09-12T18:58:21Z</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-08-26T22:00:13Z</t>
+          <t>2026-09-11T17:27:52Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-26T22:00:13Z</t>
+          <t>2026-09-11T17:27:52Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4843,11 +4843,11 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-28T15:27:27Z</t>
+          <t>2026-09-09T21:52:55Z</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98">
@@ -4901,11 +4901,11 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-29T22:05:32Z</t>
+          <t>2026-09-10T04:34:36Z</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-30T09:16:55Z</t>
+          <t>2026-09-13T05:47:33Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-08-16T16:11:04Z</t>
+          <t>2026-09-06T17:45:24Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-09-06T04:54:57Z</t>
+          <t>2026-09-12T22:30:02Z</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-08-30T10:17:25Z</t>
+          <t>2026-09-12T22:30:02Z</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -961,12 +961,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-13T02:39:48Z</t>
+          <t>2026-09-19T19:26:25Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-08T19:58:28Z</t>
+          <t>2026-09-15T21:52:04Z</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-04-28T07:12:22Z</t>
+          <t>2026-09-18T13:44:58Z</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-13T23:51:14Z</t>
+          <t>2026-09-17T06:38:12Z</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-27T03:11:19Z</t>
+          <t>2026-09-17T06:38:07Z</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-13T11:33:08Z</t>
+          <t>2026-09-20T10:58:09Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4864</v>
+        <v>4902</v>
       </c>
     </row>
     <row r="58">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-26T03:40:09Z</t>
+          <t>2026-09-13T14:33:20Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-28T06:34:58Z</t>
+          <t>2026-09-18T00:27:20Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-03T13:06:32Z</t>
+          <t>2026-09-18T17:52:29Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-15T15:40:06Z</t>
+          <t>2026-09-18T17:52:25Z</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-13T10:28:53Z</t>
+          <t>2026-09-20T09:44:10Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1183</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="79">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-28T01:46:33Z</t>
+          <t>2026-09-24T07:04:38Z</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-30T18:36:08Z</t>
+          <t>2026-09-26T18:01:13Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-12T18:15:44Z</t>
+          <t>2026-09-24T09:03:42Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-07T18:34:43Z</t>
+          <t>2026-09-25T23:01:13Z</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-27T10:38:00Z</t>
+          <t>2026-09-23T12:31:31Z</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -2635,11 +2635,11 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-20T10:58:09Z</t>
+          <t>2026-09-27T11:47:01Z</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4902</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="58">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-13T11:12:17Z</t>
+          <t>2026-09-27T11:45:51Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-13T09:41:57Z</t>
+          <t>2026-09-27T08:08:12Z</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-12T01:57:37Z</t>
+          <t>2026-09-23T12:31:09Z</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -2963,11 +2963,11 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-12T19:22:09Z</t>
+          <t>2026-09-25T17:28:04Z</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-18T00:27:20Z</t>
+          <t>2026-09-26T17:29:52Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-07T08:51:10Z</t>
+          <t>2026-09-26T20:43:28Z</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-13T11:29:36Z</t>
+          <t>2026-09-27T11:17:32Z</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67">
@@ -3183,11 +3183,11 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-13T11:29:36Z</t>
+          <t>2026-09-27T11:17:32Z</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-10T07:30:34Z</t>
+          <t>2026-09-23T12:31:08Z</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-29T02:10:25Z</t>
+          <t>2026-09-24T07:04:23Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-13T00:51:49Z</t>
+          <t>2026-09-27T11:38:18Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-12T12:39:59Z</t>
+          <t>2026-09-25T16:33:50Z</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -3411,11 +3411,11 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-13T05:42:32Z</t>
+          <t>2026-09-27T10:24:52Z</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72">
@@ -3465,11 +3465,11 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-13T09:42:36Z</t>
+          <t>2026-09-27T07:55:13Z</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-13T10:42:07Z</t>
+          <t>2026-09-26T09:20:31Z</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-13T10:40:04Z</t>
+          <t>2026-09-27T10:45:28Z</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-12-02T20:55:29Z</t>
+          <t>2026-09-23T12:31:11Z</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-13T15:02:42Z</t>
+          <t>2026-09-23T12:31:03Z</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-04T07:02:36Z</t>
+          <t>2026-09-23T12:31:02Z</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-25T05:45:12Z</t>
+          <t>2026-09-23T12:30:59Z</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-18T17:52:29Z</t>
+          <t>2026-09-26T12:53:05Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-18T17:52:25Z</t>
+          <t>2026-09-25T22:59:33Z</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-20T09:44:10Z</t>
+          <t>2026-09-27T10:48:38Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1230</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="79">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-12T17:39:19Z</t>
+          <t>2026-09-23T08:33:50Z</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -3901,11 +3901,11 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-13T08:38:23Z</t>
+          <t>2026-09-27T05:49:13Z</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81">
@@ -3955,11 +3955,11 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-12T17:52:41Z</t>
+          <t>2026-09-22T17:37:26Z</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -4009,11 +4009,11 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-10T10:56:15Z</t>
+          <t>2026-09-24T17:05:28Z</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-11T01:17:35Z</t>
+          <t>2026-09-26T17:03:41Z</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-04-28T21:58:57Z</t>
+          <t>2026-09-24T10:47:42Z</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4117,11 +4117,11 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-13T08:09:59Z</t>
+          <t>2026-09-27T10:24:28Z</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-12T17:48:03Z</t>
+          <t>2026-09-25T14:23:07Z</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-11T16:05:24Z</t>
+          <t>2026-09-27T02:02:49Z</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-08T03:34:53Z</t>
+          <t>2026-09-26T03:16:43Z</t>
         </is>
       </c>
       <c r="L88" t="n">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-05T19:56:54Z</t>
+          <t>2026-09-23T12:31:12Z</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-09-12T21:23:03Z</t>
+          <t>2026-09-26T15:30:58Z</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="90">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-04T00:04:32Z</t>
+          <t>2026-09-26T12:52:54Z</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-13T07:37:37Z</t>
+          <t>2026-09-27T04:05:04Z</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="91">
@@ -4503,11 +4503,11 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-13T07:02:11Z</t>
+          <t>2026-09-27T10:38:59Z</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="92">
@@ -4557,11 +4557,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-13T09:27:29Z</t>
+          <t>2026-09-27T11:47:09Z</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-12T20:21:58Z</t>
+          <t>2026-09-27T10:20:17Z</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -4669,11 +4669,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-12T18:58:21Z</t>
+          <t>2026-09-25T15:47:23Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-09-11T17:27:52Z</t>
+          <t>2026-09-26T22:47:01Z</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-09-11T17:27:52Z</t>
+          <t>2026-09-26T22:47:01Z</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-09-09T21:52:55Z</t>
+          <t>2026-09-27T09:19:11Z</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-09-10T04:34:36Z</t>
+          <t>2026-09-24T20:16:56Z</t>
         </is>
       </c>
       <c r="L98" t="n">
@@ -4955,11 +4955,11 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-09-13T05:47:33Z</t>
+          <t>2026-09-27T02:02:59Z</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="100">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-09-06T17:45:24Z</t>
+          <t>2026-09-17T17:57:41Z</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-05T21:47:20Z</t>
+          <t>2026-09-22T16:12:51Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-09-12T22:30:02Z</t>
+          <t>2026-09-27T07:30:40Z</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-09-12T22:30:02Z</t>
+          <t>2026-09-27T07:30:40Z</t>
         </is>
       </c>
       <c r="L102" t="n">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -685,12 +685,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-04T04:28:00Z</t>
+          <t>2026-09-29T21:07:13Z</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04T04:27:41Z</t>
+          <t>2026-09-29T21:07:08Z</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -961,12 +961,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-19T19:26:25Z</t>
+          <t>2026-09-30T23:16:45Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-15T21:52:04Z</t>
+          <t>2026-09-30T23:16:42Z</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024-08-16T22:18:57Z</t>
+          <t>2026-09-27T23:38:20Z</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-23T02:25:30Z</t>
+          <t>2026-09-30T09:03:10Z</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-26T12:53:05Z</t>
+          <t>2026-10-03T01:59:53Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-27T10:48:38Z</t>
+          <t>2026-10-04T12:07:58Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1243</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="79">

--- a/pinokio_repos.xlsx
+++ b/pinokio_repos.xlsx
@@ -961,12 +961,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-30T23:16:45Z</t>
+          <t>2026-10-07T19:19:07Z</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-30T23:16:42Z</t>
+          <t>2026-10-04T23:55:50Z</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -997,7 +997,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-05-16T10:54:13Z</t>
+          <t>2026-10-07T12:46:38Z</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-20T23:47:42Z</t>
+          <t>2026-10-05T11:09:48Z</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-13T15:47:29Z</t>
+          <t>2026-10-11T04:13:22Z</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2747,11 +2747,11 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-27T11:45:51Z</t>
+          <t>2026-10-11T09:00:51Z</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-09-13T14:33:20Z</t>
+          <t>2026-10-07T14:28:17Z</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-26T17:29:52Z</t>
+          <t>2026-10-11T07:56:39Z</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-24T07:04:23Z</t>
+          <t>2026-10-06T18:38:02Z</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-27T11:38:18Z</t>
+          <t>2026-10-11T08:59:10Z</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-04-28T23:29:48Z</t>
+          <t>2026-10-05T14:48:39Z</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-27T07:55:13Z</t>
+          <t>2026-10-11T11:20:41Z</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-03T01:59:53Z</t>
+          <t>2026-10-09T06:47:22Z</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-25T22:59:33Z</t>
+          <t>2026-10-08T19:59:30Z</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-10-04T12:07:58Z</t>
+          <t>2026-10-11T11:16:18Z</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1253</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="79">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-16T19:02:26Z</t>
+          <t>2026-10-06T06:22:34Z</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4669,11 +4669,11 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-25T15:47:23Z</t>
+          <t>2026-10-10T12:57:00Z</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-09-22T16:12:51Z</t>
+          <t>2026-10-07T17:23:49Z</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5063,11 +5063,11 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-09-27T07:30:40Z</t>
+          <t>2026-10-11T10:09:27Z</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102">
